--- a/artfynd/A 31984-2024 artfynd.xlsx
+++ b/artfynd/A 31984-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>119873228</v>
+        <v>119873578</v>
       </c>
       <c r="B2" t="n">
-        <v>91863</v>
+        <v>91840</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5966</v>
+        <v>4364</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -750,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>16:07</t>
+          <t>16:18</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +760,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>16:07</t>
+          <t>16:18</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>119873578</v>
+        <v>119875141</v>
       </c>
       <c r="B3" t="n">
-        <v>91840</v>
+        <v>91832</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -799,41 +799,41 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>4364</v>
+        <v>4361</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Aftonmorberget, Vb</t>
+          <t>Aftonmorberget, Aftonmorberget, Vb</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>780183</v>
+        <v>780192</v>
       </c>
       <c r="R3" t="n">
-        <v>7132600</v>
+        <v>7132672</v>
       </c>
       <c r="S3" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -862,7 +862,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>16:18</t>
+          <t>17:31</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -872,7 +872,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>16:18</t>
+          <t>17:31</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -899,10 +899,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>119874337</v>
+        <v>119874570</v>
       </c>
       <c r="B4" t="n">
-        <v>91863</v>
+        <v>91840</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -911,25 +911,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5966</v>
+        <v>4364</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -939,10 +939,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>780128</v>
+        <v>780092</v>
       </c>
       <c r="R4" t="n">
-        <v>7132633</v>
+        <v>7132657</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -974,7 +974,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>16:52</t>
+          <t>17:06</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>16:52</t>
+          <t>17:06</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1235,14 +1235,14 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>119874233</v>
+        <v>119873228</v>
       </c>
       <c r="B7" t="n">
         <v>91863</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Godkänd. Foto (eller ljud) granskat av validerare</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1271,17 +1271,17 @@
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Aftonmorberget, Aftonmorberget, Vb</t>
+          <t>Aftonmorberget, Vb</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>780119</v>
+        <v>780183</v>
       </c>
       <c r="R7" t="n">
-        <v>7132631</v>
+        <v>7132600</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1310,7 +1310,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>16:50</t>
+          <t>16:07</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1320,7 +1320,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>16:50</t>
+          <t>16:07</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1347,37 +1347,37 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>119874570</v>
+        <v>119874233</v>
       </c>
       <c r="B8" t="n">
-        <v>91840</v>
+        <v>91863</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Godkänd. Foto (eller ljud) granskat av validerare</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>4364</v>
+        <v>5966</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1387,10 +1387,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>780092</v>
+        <v>780119</v>
       </c>
       <c r="R8" t="n">
-        <v>7132657</v>
+        <v>7132631</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1422,7 +1422,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>17:06</t>
+          <t>16:50</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1432,7 +1432,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>17:06</t>
+          <t>16:50</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1459,14 +1459,14 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>119875141</v>
+        <v>119874337</v>
       </c>
       <c r="B9" t="n">
-        <v>91832</v>
+        <v>91863</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Godkänd. Foto (eller ljud) granskat av validerare</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1475,21 +1475,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>4361</v>
+        <v>5966</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1499,10 +1499,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>780192</v>
+        <v>780128</v>
       </c>
       <c r="R9" t="n">
-        <v>7132672</v>
+        <v>7132633</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1534,7 +1534,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>17:31</t>
+          <t>16:52</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1544,7 +1544,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>17:31</t>
+          <t>16:52</t>
         </is>
       </c>
       <c r="AD9" t="b">

--- a/artfynd/A 31984-2024 artfynd.xlsx
+++ b/artfynd/A 31984-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>119873578</v>
+        <v>119874364</v>
       </c>
       <c r="B2" t="n">
-        <v>91840</v>
+        <v>91832</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,41 +687,41 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>4364</v>
+        <v>4361</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Aftonmorberget, Vb</t>
+          <t>Aftonmorberget, Aftonmorberget, Vb</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>780183</v>
+        <v>780128</v>
       </c>
       <c r="R2" t="n">
-        <v>7132600</v>
+        <v>7132633</v>
       </c>
       <c r="S2" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -750,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>16:18</t>
+          <t>16:55</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +760,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>16:18</t>
+          <t>16:55</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>119875141</v>
+        <v>119874570</v>
       </c>
       <c r="B3" t="n">
-        <v>91832</v>
+        <v>91840</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -799,25 +799,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>4361</v>
+        <v>4364</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -827,10 +827,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>780192</v>
+        <v>780092</v>
       </c>
       <c r="R3" t="n">
-        <v>7132672</v>
+        <v>7132657</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -862,7 +862,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>17:31</t>
+          <t>17:06</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -872,7 +872,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>17:31</t>
+          <t>17:06</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -899,10 +899,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>119874570</v>
+        <v>119875141</v>
       </c>
       <c r="B4" t="n">
-        <v>91840</v>
+        <v>91832</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -911,25 +911,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>4364</v>
+        <v>4361</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -939,10 +939,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>780092</v>
+        <v>780192</v>
       </c>
       <c r="R4" t="n">
-        <v>7132657</v>
+        <v>7132672</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -974,7 +974,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>17:06</t>
+          <t>17:31</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>17:06</t>
+          <t>17:31</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1123,10 +1123,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>119874364</v>
+        <v>119873578</v>
       </c>
       <c r="B6" t="n">
-        <v>91832</v>
+        <v>91840</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1135,41 +1135,41 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>4361</v>
+        <v>4364</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Aftonmorberget, Aftonmorberget, Vb</t>
+          <t>Aftonmorberget, Vb</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>780128</v>
+        <v>780183</v>
       </c>
       <c r="R6" t="n">
-        <v>7132633</v>
+        <v>7132600</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1198,7 +1198,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>16:55</t>
+          <t>16:18</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1208,7 +1208,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>16:55</t>
+          <t>16:18</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1235,7 +1235,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>119873228</v>
+        <v>119874337</v>
       </c>
       <c r="B7" t="n">
         <v>91863</v>
@@ -1271,17 +1271,17 @@
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Aftonmorberget, Vb</t>
+          <t>Aftonmorberget, Aftonmorberget, Vb</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>780183</v>
+        <v>780128</v>
       </c>
       <c r="R7" t="n">
-        <v>7132600</v>
+        <v>7132633</v>
       </c>
       <c r="S7" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1310,7 +1310,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>16:07</t>
+          <t>16:52</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1320,7 +1320,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>16:07</t>
+          <t>16:52</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1347,7 +1347,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>119874233</v>
+        <v>119873228</v>
       </c>
       <c r="B8" t="n">
         <v>91863</v>
@@ -1383,17 +1383,17 @@
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Aftonmorberget, Aftonmorberget, Vb</t>
+          <t>Aftonmorberget, Vb</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>780119</v>
+        <v>780183</v>
       </c>
       <c r="R8" t="n">
-        <v>7132631</v>
+        <v>7132600</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1422,7 +1422,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>16:50</t>
+          <t>16:07</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1432,7 +1432,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>16:50</t>
+          <t>16:07</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1459,7 +1459,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>119874337</v>
+        <v>119874233</v>
       </c>
       <c r="B9" t="n">
         <v>91863</v>
@@ -1499,10 +1499,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>780128</v>
+        <v>780119</v>
       </c>
       <c r="R9" t="n">
-        <v>7132633</v>
+        <v>7132631</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1534,7 +1534,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>16:52</t>
+          <t>16:50</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1544,7 +1544,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>16:52</t>
+          <t>16:50</t>
         </is>
       </c>
       <c r="AD9" t="b">

--- a/artfynd/A 31984-2024 artfynd.xlsx
+++ b/artfynd/A 31984-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>119874364</v>
+        <v>119874570</v>
       </c>
       <c r="B2" t="n">
-        <v>91832</v>
+        <v>91840</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>4361</v>
+        <v>4364</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>780128</v>
+        <v>780092</v>
       </c>
       <c r="R2" t="n">
-        <v>7132633</v>
+        <v>7132657</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -750,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>16:55</t>
+          <t>17:06</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +760,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>16:55</t>
+          <t>17:06</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,7 +787,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>119874570</v>
+        <v>119873578</v>
       </c>
       <c r="B3" t="n">
         <v>91840</v>
@@ -823,17 +823,17 @@
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Aftonmorberget, Aftonmorberget, Vb</t>
+          <t>Aftonmorberget, Vb</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>780092</v>
+        <v>780183</v>
       </c>
       <c r="R3" t="n">
-        <v>7132657</v>
+        <v>7132600</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -862,7 +862,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>17:06</t>
+          <t>16:18</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -872,7 +872,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>17:06</t>
+          <t>16:18</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -899,10 +899,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>119875141</v>
+        <v>119873052</v>
       </c>
       <c r="B4" t="n">
-        <v>91832</v>
+        <v>91884</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -915,21 +915,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>4361</v>
+        <v>5449</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -939,10 +939,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>780192</v>
+        <v>780239</v>
       </c>
       <c r="R4" t="n">
-        <v>7132672</v>
+        <v>7132630</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -974,7 +974,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>17:31</t>
+          <t>15:55</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>17:31</t>
+          <t>15:55</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1011,10 +1011,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>119873052</v>
+        <v>119875141</v>
       </c>
       <c r="B5" t="n">
-        <v>91884</v>
+        <v>91832</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1027,21 +1027,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5449</v>
+        <v>4361</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1051,10 +1051,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>780239</v>
+        <v>780192</v>
       </c>
       <c r="R5" t="n">
-        <v>7132630</v>
+        <v>7132672</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1086,7 +1086,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>15:55</t>
+          <t>17:31</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>15:55</t>
+          <t>17:31</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1123,10 +1123,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>119873578</v>
+        <v>119874364</v>
       </c>
       <c r="B6" t="n">
-        <v>91840</v>
+        <v>91832</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1135,41 +1135,41 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>4364</v>
+        <v>4361</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Aftonmorberget, Vb</t>
+          <t>Aftonmorberget, Aftonmorberget, Vb</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>780183</v>
+        <v>780128</v>
       </c>
       <c r="R6" t="n">
-        <v>7132600</v>
+        <v>7132633</v>
       </c>
       <c r="S6" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1198,7 +1198,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>16:18</t>
+          <t>16:55</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1208,7 +1208,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>16:18</t>
+          <t>16:55</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1235,7 +1235,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>119874337</v>
+        <v>119874233</v>
       </c>
       <c r="B7" t="n">
         <v>91863</v>
@@ -1275,10 +1275,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>780128</v>
+        <v>780119</v>
       </c>
       <c r="R7" t="n">
-        <v>7132633</v>
+        <v>7132631</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1310,7 +1310,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>16:52</t>
+          <t>16:50</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1320,7 +1320,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>16:52</t>
+          <t>16:50</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1347,7 +1347,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>119873228</v>
+        <v>119874337</v>
       </c>
       <c r="B8" t="n">
         <v>91863</v>
@@ -1383,17 +1383,17 @@
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Aftonmorberget, Vb</t>
+          <t>Aftonmorberget, Aftonmorberget, Vb</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>780183</v>
+        <v>780128</v>
       </c>
       <c r="R8" t="n">
-        <v>7132600</v>
+        <v>7132633</v>
       </c>
       <c r="S8" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1422,7 +1422,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>16:07</t>
+          <t>16:52</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1432,7 +1432,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>16:07</t>
+          <t>16:52</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1459,7 +1459,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>119874233</v>
+        <v>119873228</v>
       </c>
       <c r="B9" t="n">
         <v>91863</v>
@@ -1495,17 +1495,17 @@
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Aftonmorberget, Aftonmorberget, Vb</t>
+          <t>Aftonmorberget, Vb</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>780119</v>
+        <v>780183</v>
       </c>
       <c r="R9" t="n">
-        <v>7132631</v>
+        <v>7132600</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1534,7 +1534,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>16:50</t>
+          <t>16:07</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1544,7 +1544,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>16:50</t>
+          <t>16:07</t>
         </is>
       </c>
       <c r="AD9" t="b">

--- a/artfynd/A 31984-2024 artfynd.xlsx
+++ b/artfynd/A 31984-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>119874570</v>
       </c>
       <c r="B2" t="n">
-        <v>91840</v>
+        <v>91858</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -787,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>119873578</v>
+        <v>119875141</v>
       </c>
       <c r="B3" t="n">
-        <v>91840</v>
+        <v>91850</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -799,41 +799,41 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>4364</v>
+        <v>4361</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Aftonmorberget, Vb</t>
+          <t>Aftonmorberget, Aftonmorberget, Vb</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>780183</v>
+        <v>780192</v>
       </c>
       <c r="R3" t="n">
-        <v>7132600</v>
+        <v>7132672</v>
       </c>
       <c r="S3" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -862,7 +862,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>16:18</t>
+          <t>17:31</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -872,7 +872,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>16:18</t>
+          <t>17:31</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -899,10 +899,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>119873052</v>
+        <v>119873578</v>
       </c>
       <c r="B4" t="n">
-        <v>91884</v>
+        <v>91858</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -911,41 +911,41 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5449</v>
+        <v>4364</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Aftonmorberget, Aftonmorberget, Vb</t>
+          <t>Aftonmorberget, Vb</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>780239</v>
+        <v>780183</v>
       </c>
       <c r="R4" t="n">
-        <v>7132630</v>
+        <v>7132600</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -974,7 +974,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>15:55</t>
+          <t>16:18</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>15:55</t>
+          <t>16:18</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1011,10 +1011,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>119875141</v>
+        <v>119873052</v>
       </c>
       <c r="B5" t="n">
-        <v>91832</v>
+        <v>91902</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1027,21 +1027,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>4361</v>
+        <v>5449</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1051,10 +1051,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>780192</v>
+        <v>780239</v>
       </c>
       <c r="R5" t="n">
-        <v>7132672</v>
+        <v>7132630</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1086,7 +1086,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>17:31</t>
+          <t>15:55</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>17:31</t>
+          <t>15:55</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1126,7 +1126,7 @@
         <v>119874364</v>
       </c>
       <c r="B6" t="n">
-        <v>91832</v>
+        <v>91850</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1235,10 +1235,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>119874233</v>
+        <v>119874337</v>
       </c>
       <c r="B7" t="n">
-        <v>91863</v>
+        <v>91881</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1275,10 +1275,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>780119</v>
+        <v>780128</v>
       </c>
       <c r="R7" t="n">
-        <v>7132631</v>
+        <v>7132633</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1310,7 +1310,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>16:50</t>
+          <t>16:52</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1320,7 +1320,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>16:50</t>
+          <t>16:52</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1347,10 +1347,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>119874337</v>
+        <v>119873228</v>
       </c>
       <c r="B8" t="n">
-        <v>91863</v>
+        <v>91881</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1383,17 +1383,17 @@
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Aftonmorberget, Aftonmorberget, Vb</t>
+          <t>Aftonmorberget, Vb</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>780128</v>
+        <v>780183</v>
       </c>
       <c r="R8" t="n">
-        <v>7132633</v>
+        <v>7132600</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1422,7 +1422,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>16:52</t>
+          <t>16:07</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1432,7 +1432,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>16:52</t>
+          <t>16:07</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1459,10 +1459,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>119873228</v>
+        <v>119874233</v>
       </c>
       <c r="B9" t="n">
-        <v>91863</v>
+        <v>91881</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1495,17 +1495,17 @@
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Aftonmorberget, Vb</t>
+          <t>Aftonmorberget, Aftonmorberget, Vb</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>780183</v>
+        <v>780119</v>
       </c>
       <c r="R9" t="n">
-        <v>7132600</v>
+        <v>7132631</v>
       </c>
       <c r="S9" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1534,7 +1534,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>16:07</t>
+          <t>16:50</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1544,7 +1544,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>16:07</t>
+          <t>16:50</t>
         </is>
       </c>
       <c r="AD9" t="b">

--- a/artfynd/A 31984-2024 artfynd.xlsx
+++ b/artfynd/A 31984-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>119874570</v>
+        <v>119874364</v>
       </c>
       <c r="B2" t="n">
-        <v>91858</v>
+        <v>91850</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>4364</v>
+        <v>4361</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>780092</v>
+        <v>780128</v>
       </c>
       <c r="R2" t="n">
-        <v>7132657</v>
+        <v>7132633</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -750,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>17:06</t>
+          <t>16:55</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +760,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>17:06</t>
+          <t>16:55</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>119875141</v>
+        <v>119874570</v>
       </c>
       <c r="B3" t="n">
-        <v>91850</v>
+        <v>91858</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -799,25 +799,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>4361</v>
+        <v>4364</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -827,10 +827,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>780192</v>
+        <v>780092</v>
       </c>
       <c r="R3" t="n">
-        <v>7132672</v>
+        <v>7132657</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -862,7 +862,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>17:31</t>
+          <t>17:06</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -872,7 +872,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>17:31</t>
+          <t>17:06</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -1011,10 +1011,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>119873052</v>
+        <v>119875141</v>
       </c>
       <c r="B5" t="n">
-        <v>91902</v>
+        <v>91850</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1027,21 +1027,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5449</v>
+        <v>4361</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1051,10 +1051,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>780239</v>
+        <v>780192</v>
       </c>
       <c r="R5" t="n">
-        <v>7132630</v>
+        <v>7132672</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1086,7 +1086,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>15:55</t>
+          <t>17:31</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>15:55</t>
+          <t>17:31</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1123,10 +1123,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>119874364</v>
+        <v>119873052</v>
       </c>
       <c r="B6" t="n">
-        <v>91850</v>
+        <v>91902</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1139,21 +1139,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>4361</v>
+        <v>5449</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1163,10 +1163,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>780128</v>
+        <v>780239</v>
       </c>
       <c r="R6" t="n">
-        <v>7132633</v>
+        <v>7132630</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1198,7 +1198,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>16:55</t>
+          <t>15:55</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1208,7 +1208,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>16:55</t>
+          <t>15:55</t>
         </is>
       </c>
       <c r="AD6" t="b">

--- a/artfynd/A 31984-2024 artfynd.xlsx
+++ b/artfynd/A 31984-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>119874364</v>
+        <v>119873338</v>
       </c>
       <c r="B2" t="n">
-        <v>91850</v>
+        <v>91858</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,41 +687,41 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>4361</v>
+        <v>4364</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Aftonmorberget, Aftonmorberget, Vb</t>
+          <t>Aftonmorberget, Vb</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>780128</v>
+        <v>780183</v>
       </c>
       <c r="R2" t="n">
-        <v>7132633</v>
+        <v>7132600</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -750,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>16:55</t>
+          <t>16:12</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +760,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>16:55</t>
+          <t>16:12</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -899,10 +899,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>119873578</v>
+        <v>119873052</v>
       </c>
       <c r="B4" t="n">
-        <v>91858</v>
+        <v>91902</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -911,41 +911,41 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>4364</v>
+        <v>5449</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Aftonmorberget, Vb</t>
+          <t>Aftonmorberget, Aftonmorberget, Vb</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>780183</v>
+        <v>780239</v>
       </c>
       <c r="R4" t="n">
-        <v>7132600</v>
+        <v>7132630</v>
       </c>
       <c r="S4" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -974,7 +974,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>16:18</t>
+          <t>15:55</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>16:18</t>
+          <t>15:55</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1011,7 +1011,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>119875141</v>
+        <v>119874364</v>
       </c>
       <c r="B5" t="n">
         <v>91850</v>
@@ -1051,10 +1051,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>780192</v>
+        <v>780128</v>
       </c>
       <c r="R5" t="n">
-        <v>7132672</v>
+        <v>7132633</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1086,7 +1086,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>17:31</t>
+          <t>16:55</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>17:31</t>
+          <t>16:55</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1123,10 +1123,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>119873052</v>
+        <v>119875141</v>
       </c>
       <c r="B6" t="n">
-        <v>91902</v>
+        <v>91850</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1139,21 +1139,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5449</v>
+        <v>4361</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1163,10 +1163,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>780239</v>
+        <v>780192</v>
       </c>
       <c r="R6" t="n">
-        <v>7132630</v>
+        <v>7132672</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1198,7 +1198,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>15:55</t>
+          <t>17:31</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1208,7 +1208,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>15:55</t>
+          <t>17:31</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1347,7 +1347,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>119873228</v>
+        <v>119874233</v>
       </c>
       <c r="B8" t="n">
         <v>91881</v>
@@ -1383,17 +1383,17 @@
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Aftonmorberget, Vb</t>
+          <t>Aftonmorberget, Aftonmorberget, Vb</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>780183</v>
+        <v>780119</v>
       </c>
       <c r="R8" t="n">
-        <v>7132600</v>
+        <v>7132631</v>
       </c>
       <c r="S8" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1422,7 +1422,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>16:07</t>
+          <t>16:50</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1432,7 +1432,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>16:07</t>
+          <t>16:50</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1459,7 +1459,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>119874233</v>
+        <v>119873228</v>
       </c>
       <c r="B9" t="n">
         <v>91881</v>
@@ -1495,17 +1495,17 @@
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Aftonmorberget, Aftonmorberget, Vb</t>
+          <t>Aftonmorberget, Vb</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>780119</v>
+        <v>780183</v>
       </c>
       <c r="R9" t="n">
-        <v>7132631</v>
+        <v>7132600</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1534,7 +1534,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>16:50</t>
+          <t>16:07</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1544,7 +1544,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>16:50</t>
+          <t>16:07</t>
         </is>
       </c>
       <c r="AD9" t="b">

--- a/artfynd/A 31984-2024 artfynd.xlsx
+++ b/artfynd/A 31984-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>119873338</v>
+        <v>119875141</v>
       </c>
       <c r="B2" t="n">
-        <v>91858</v>
+        <v>91850</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,41 +687,41 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>4364</v>
+        <v>4361</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Aftonmorberget, Vb</t>
+          <t>Aftonmorberget, Aftonmorberget, Vb</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>780183</v>
+        <v>780192</v>
       </c>
       <c r="R2" t="n">
-        <v>7132600</v>
+        <v>7132672</v>
       </c>
       <c r="S2" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -750,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>16:12</t>
+          <t>17:31</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +760,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>16:12</t>
+          <t>17:31</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>119874570</v>
+        <v>119873052</v>
       </c>
       <c r="B3" t="n">
-        <v>91858</v>
+        <v>91902</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -799,25 +799,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>4364</v>
+        <v>5449</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -827,10 +827,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>780092</v>
+        <v>780239</v>
       </c>
       <c r="R3" t="n">
-        <v>7132657</v>
+        <v>7132630</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -862,7 +862,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>17:06</t>
+          <t>15:55</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -872,7 +872,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>17:06</t>
+          <t>15:55</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -899,10 +899,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>119873052</v>
+        <v>119874570</v>
       </c>
       <c r="B4" t="n">
-        <v>91902</v>
+        <v>91858</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -911,25 +911,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5449</v>
+        <v>4364</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -939,10 +939,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>780239</v>
+        <v>780092</v>
       </c>
       <c r="R4" t="n">
-        <v>7132630</v>
+        <v>7132657</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -974,7 +974,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>15:55</t>
+          <t>17:06</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>15:55</t>
+          <t>17:06</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1123,10 +1123,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>119875141</v>
+        <v>119873338</v>
       </c>
       <c r="B6" t="n">
-        <v>91850</v>
+        <v>91858</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1135,41 +1135,41 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>4361</v>
+        <v>4364</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Aftonmorberget, Aftonmorberget, Vb</t>
+          <t>Aftonmorberget, Vb</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>780192</v>
+        <v>780183</v>
       </c>
       <c r="R6" t="n">
-        <v>7132672</v>
+        <v>7132600</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1198,7 +1198,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>17:31</t>
+          <t>16:12</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1208,7 +1208,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>17:31</t>
+          <t>16:12</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1235,7 +1235,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>119874337</v>
+        <v>119874233</v>
       </c>
       <c r="B7" t="n">
         <v>91881</v>
@@ -1275,10 +1275,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>780128</v>
+        <v>780119</v>
       </c>
       <c r="R7" t="n">
-        <v>7132633</v>
+        <v>7132631</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1310,7 +1310,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>16:52</t>
+          <t>16:50</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1320,7 +1320,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>16:52</t>
+          <t>16:50</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1347,7 +1347,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>119874233</v>
+        <v>119873228</v>
       </c>
       <c r="B8" t="n">
         <v>91881</v>
@@ -1383,17 +1383,17 @@
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Aftonmorberget, Aftonmorberget, Vb</t>
+          <t>Aftonmorberget, Vb</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>780119</v>
+        <v>780183</v>
       </c>
       <c r="R8" t="n">
-        <v>7132631</v>
+        <v>7132600</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1422,7 +1422,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>16:50</t>
+          <t>16:07</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1432,7 +1432,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>16:50</t>
+          <t>16:07</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1459,7 +1459,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>119873228</v>
+        <v>119874337</v>
       </c>
       <c r="B9" t="n">
         <v>91881</v>
@@ -1495,17 +1495,17 @@
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Aftonmorberget, Vb</t>
+          <t>Aftonmorberget, Aftonmorberget, Vb</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>780183</v>
+        <v>780128</v>
       </c>
       <c r="R9" t="n">
-        <v>7132600</v>
+        <v>7132633</v>
       </c>
       <c r="S9" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1534,7 +1534,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>16:07</t>
+          <t>16:52</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1544,7 +1544,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>16:07</t>
+          <t>16:52</t>
         </is>
       </c>
       <c r="AD9" t="b">

--- a/artfynd/A 31984-2024 artfynd.xlsx
+++ b/artfynd/A 31984-2024 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>119875141</v>
+        <v>119874364</v>
       </c>
       <c r="B2" t="n">
         <v>91850</v>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>780192</v>
+        <v>780128</v>
       </c>
       <c r="R2" t="n">
-        <v>7132672</v>
+        <v>7132633</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -750,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>17:31</t>
+          <t>16:55</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +760,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>17:31</t>
+          <t>16:55</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>119873052</v>
+        <v>119873338</v>
       </c>
       <c r="B3" t="n">
-        <v>91902</v>
+        <v>91858</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -799,41 +799,41 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5449</v>
+        <v>4364</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Aftonmorberget, Aftonmorberget, Vb</t>
+          <t>Aftonmorberget, Vb</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>780239</v>
+        <v>780183</v>
       </c>
       <c r="R3" t="n">
-        <v>7132630</v>
+        <v>7132600</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -862,7 +862,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>15:55</t>
+          <t>16:12</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -872,7 +872,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>15:55</t>
+          <t>16:12</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -1011,7 +1011,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>119874364</v>
+        <v>119875141</v>
       </c>
       <c r="B5" t="n">
         <v>91850</v>
@@ -1051,10 +1051,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>780128</v>
+        <v>780192</v>
       </c>
       <c r="R5" t="n">
-        <v>7132633</v>
+        <v>7132672</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1086,7 +1086,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>16:55</t>
+          <t>17:31</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>16:55</t>
+          <t>17:31</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1123,10 +1123,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>119873338</v>
+        <v>119873052</v>
       </c>
       <c r="B6" t="n">
-        <v>91858</v>
+        <v>91902</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1135,41 +1135,41 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>4364</v>
+        <v>5449</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Aftonmorberget, Vb</t>
+          <t>Aftonmorberget, Aftonmorberget, Vb</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>780183</v>
+        <v>780239</v>
       </c>
       <c r="R6" t="n">
-        <v>7132600</v>
+        <v>7132630</v>
       </c>
       <c r="S6" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1198,7 +1198,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>16:12</t>
+          <t>15:55</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1208,7 +1208,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>16:12</t>
+          <t>15:55</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1235,7 +1235,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>119874233</v>
+        <v>119874337</v>
       </c>
       <c r="B7" t="n">
         <v>91881</v>
@@ -1275,10 +1275,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>780119</v>
+        <v>780128</v>
       </c>
       <c r="R7" t="n">
-        <v>7132631</v>
+        <v>7132633</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1310,7 +1310,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>16:50</t>
+          <t>16:52</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1320,7 +1320,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>16:50</t>
+          <t>16:52</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1459,7 +1459,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>119874337</v>
+        <v>119874233</v>
       </c>
       <c r="B9" t="n">
         <v>91881</v>
@@ -1499,10 +1499,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>780128</v>
+        <v>780119</v>
       </c>
       <c r="R9" t="n">
-        <v>7132633</v>
+        <v>7132631</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1534,7 +1534,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>16:52</t>
+          <t>16:50</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1544,7 +1544,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>16:52</t>
+          <t>16:50</t>
         </is>
       </c>
       <c r="AD9" t="b">

--- a/artfynd/A 31984-2024 artfynd.xlsx
+++ b/artfynd/A 31984-2024 artfynd.xlsx
@@ -1235,7 +1235,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>119874337</v>
+        <v>119873228</v>
       </c>
       <c r="B7" t="n">
         <v>91881</v>
@@ -1271,17 +1271,17 @@
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Aftonmorberget, Aftonmorberget, Vb</t>
+          <t>Aftonmorberget, Vb</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>780128</v>
+        <v>780183</v>
       </c>
       <c r="R7" t="n">
-        <v>7132633</v>
+        <v>7132600</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1310,7 +1310,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>16:52</t>
+          <t>16:07</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1320,7 +1320,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>16:52</t>
+          <t>16:07</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1347,7 +1347,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>119873228</v>
+        <v>119874337</v>
       </c>
       <c r="B8" t="n">
         <v>91881</v>
@@ -1383,17 +1383,17 @@
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Aftonmorberget, Vb</t>
+          <t>Aftonmorberget, Aftonmorberget, Vb</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>780183</v>
+        <v>780128</v>
       </c>
       <c r="R8" t="n">
-        <v>7132600</v>
+        <v>7132633</v>
       </c>
       <c r="S8" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1422,7 +1422,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>16:07</t>
+          <t>16:52</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1432,7 +1432,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>16:07</t>
+          <t>16:52</t>
         </is>
       </c>
       <c r="AD8" t="b">
